--- a/storage/templates/Comedor.xlsx
+++ b/storage/templates/Comedor.xlsx
@@ -371,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -476,6 +476,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -806,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN1003"/>
+  <dimension ref="A1:AN1008"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="25.05" customHeight="1"/>
   <cols>
     <col width="10.77734375" customWidth="1" style="1" min="1" max="1"/>
@@ -6320,221 +6323,370 @@
       </c>
     </row>
     <row r="83" ht="25.05" customHeight="1">
-      <c r="C83" s="3">
-        <f>SUM(C7:C82)</f>
-        <v/>
-      </c>
-      <c r="D83" s="9" t="n"/>
-      <c r="E83" s="10" t="inlineStr">
+      <c r="A83" s="37" t="inlineStr">
+        <is>
+          <t>6913</t>
+        </is>
+      </c>
+      <c r="B83" s="37" t="inlineStr">
+        <is>
+          <t>VINO RDO RENE BARBIER MEDITERRANEAN 75 CL</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="38" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>2.12516</v>
+      </c>
+      <c r="F83" s="20">
+        <f>C83*E83</f>
+        <v/>
+      </c>
+      <c r="G83" s="19" t="n"/>
+      <c r="H83" s="19" t="n"/>
+      <c r="I83" s="19" t="n"/>
+      <c r="J83" s="19" t="n"/>
+      <c r="K83" s="19" t="n"/>
+      <c r="L83" s="19" t="n"/>
+      <c r="M83" s="19" t="n"/>
+      <c r="N83" s="19" t="n"/>
+      <c r="O83" s="19" t="n"/>
+      <c r="P83" s="19" t="n"/>
+      <c r="Q83" s="19" t="n"/>
+      <c r="R83" s="19" t="n"/>
+      <c r="S83" s="19" t="n"/>
+      <c r="T83" s="19" t="n"/>
+      <c r="U83" s="19" t="n"/>
+      <c r="V83" s="19" t="n"/>
+      <c r="W83" s="19" t="n"/>
+      <c r="X83" s="19" t="n"/>
+      <c r="Y83" s="19" t="n"/>
+      <c r="Z83" s="19" t="n"/>
+      <c r="AA83" s="19" t="n"/>
+      <c r="AB83" s="19" t="n"/>
+      <c r="AC83" s="19" t="n"/>
+      <c r="AD83" s="19" t="n"/>
+      <c r="AE83" s="19" t="n"/>
+      <c r="AF83" s="19" t="n"/>
+      <c r="AG83" s="19" t="n"/>
+      <c r="AH83" s="19" t="n"/>
+      <c r="AI83" s="19" t="n"/>
+      <c r="AJ83" s="19" t="n"/>
+      <c r="AK83" s="19" t="n"/>
+      <c r="AL83" s="22">
+        <f>SUM(G83:AK83)</f>
+        <v/>
+      </c>
+      <c r="AM83" s="23">
+        <f>SUM(C83,AL83)</f>
+        <v/>
+      </c>
+      <c r="AN83" s="24">
+        <f>E83*AM83</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="25.05" customHeight="1">
+      <c r="A84" s="37" t="inlineStr">
+        <is>
+          <t>10907</t>
+        </is>
+      </c>
+      <c r="B84" s="37" t="inlineStr">
+        <is>
+          <t>REFRESCO CRISTAL AQUARIUS C/R 30 CL</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="38" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.66121</v>
+      </c>
+      <c r="F84" s="20">
+        <f>C84*E84</f>
+        <v/>
+      </c>
+      <c r="G84" s="19" t="n"/>
+      <c r="H84" s="19" t="n"/>
+      <c r="I84" s="19" t="n"/>
+      <c r="J84" s="19" t="n"/>
+      <c r="K84" s="19" t="n"/>
+      <c r="L84" s="19" t="n"/>
+      <c r="M84" s="19" t="n"/>
+      <c r="N84" s="19" t="n"/>
+      <c r="O84" s="19" t="n"/>
+      <c r="P84" s="19" t="n"/>
+      <c r="Q84" s="19" t="n"/>
+      <c r="R84" s="19" t="n"/>
+      <c r="S84" s="19" t="n"/>
+      <c r="T84" s="19" t="n"/>
+      <c r="U84" s="19" t="n"/>
+      <c r="V84" s="19" t="n"/>
+      <c r="W84" s="19" t="n"/>
+      <c r="X84" s="19" t="n"/>
+      <c r="Y84" s="19" t="n"/>
+      <c r="Z84" s="19" t="n"/>
+      <c r="AA84" s="19" t="n"/>
+      <c r="AB84" s="19" t="n"/>
+      <c r="AC84" s="19" t="n"/>
+      <c r="AD84" s="19" t="n"/>
+      <c r="AE84" s="19" t="n"/>
+      <c r="AF84" s="19" t="n"/>
+      <c r="AG84" s="19" t="n"/>
+      <c r="AH84" s="19" t="n"/>
+      <c r="AI84" s="19" t="n"/>
+      <c r="AJ84" s="19" t="n"/>
+      <c r="AK84" s="19" t="n"/>
+      <c r="AL84" s="22">
+        <f>SUM(G84:AK84)</f>
+        <v/>
+      </c>
+      <c r="AM84" s="23">
+        <f>SUM(C84,AL84)</f>
+        <v/>
+      </c>
+      <c r="AN84" s="24">
+        <f>E84*AM84</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="25.05" customHeight="1">
+      <c r="A85" s="37" t="inlineStr">
+        <is>
+          <t>19838</t>
+        </is>
+      </c>
+      <c r="B85" s="37" t="inlineStr">
+        <is>
+          <t>REFRESCO CRISTAL AQUARIUS NARANJA C/R 30 CL</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="38" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.66121</v>
+      </c>
+      <c r="F85" s="20">
+        <f>C85*E85</f>
+        <v/>
+      </c>
+      <c r="G85" s="19" t="n"/>
+      <c r="H85" s="19" t="n"/>
+      <c r="I85" s="19" t="n"/>
+      <c r="J85" s="19" t="n"/>
+      <c r="K85" s="19" t="n"/>
+      <c r="L85" s="19" t="n"/>
+      <c r="M85" s="19" t="n"/>
+      <c r="N85" s="19" t="n"/>
+      <c r="O85" s="19" t="n"/>
+      <c r="P85" s="19" t="n"/>
+      <c r="Q85" s="19" t="n"/>
+      <c r="R85" s="19" t="n"/>
+      <c r="S85" s="19" t="n"/>
+      <c r="T85" s="19" t="n"/>
+      <c r="U85" s="19" t="n"/>
+      <c r="V85" s="19" t="n"/>
+      <c r="W85" s="19" t="n"/>
+      <c r="X85" s="19" t="n"/>
+      <c r="Y85" s="19" t="n"/>
+      <c r="Z85" s="19" t="n"/>
+      <c r="AA85" s="19" t="n"/>
+      <c r="AB85" s="19" t="n"/>
+      <c r="AC85" s="19" t="n"/>
+      <c r="AD85" s="19" t="n"/>
+      <c r="AE85" s="19" t="n"/>
+      <c r="AF85" s="19" t="n"/>
+      <c r="AG85" s="19" t="n"/>
+      <c r="AH85" s="19" t="n"/>
+      <c r="AI85" s="19" t="n"/>
+      <c r="AJ85" s="19" t="n"/>
+      <c r="AK85" s="19" t="n"/>
+      <c r="AL85" s="22">
+        <f>SUM(G85:AK85)</f>
+        <v/>
+      </c>
+      <c r="AM85" s="23">
+        <f>SUM(C85,AL85)</f>
+        <v/>
+      </c>
+      <c r="AN85" s="24">
+        <f>E85*AM85</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="25.05" customHeight="1">
+      <c r="A86" s="37" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="B86" s="37" t="inlineStr">
+        <is>
+          <t>REFRESCO CRISTAL BITTER KAS S/R 20 CL</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="38" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.65264</v>
+      </c>
+      <c r="F86" s="20">
+        <f>C86*E86</f>
+        <v/>
+      </c>
+      <c r="G86" s="19" t="n"/>
+      <c r="H86" s="19" t="n"/>
+      <c r="I86" s="19" t="n"/>
+      <c r="J86" s="19" t="n"/>
+      <c r="K86" s="19" t="n"/>
+      <c r="L86" s="19" t="n"/>
+      <c r="M86" s="19" t="n"/>
+      <c r="N86" s="19" t="n"/>
+      <c r="O86" s="19" t="n"/>
+      <c r="P86" s="19" t="n"/>
+      <c r="Q86" s="19" t="n"/>
+      <c r="R86" s="19" t="n"/>
+      <c r="S86" s="19" t="n"/>
+      <c r="T86" s="19" t="n"/>
+      <c r="U86" s="19" t="n"/>
+      <c r="V86" s="19" t="n"/>
+      <c r="W86" s="19" t="n"/>
+      <c r="X86" s="19" t="n"/>
+      <c r="Y86" s="19" t="n"/>
+      <c r="Z86" s="19" t="n"/>
+      <c r="AA86" s="19" t="n"/>
+      <c r="AB86" s="19" t="n"/>
+      <c r="AC86" s="19" t="n"/>
+      <c r="AD86" s="19" t="n"/>
+      <c r="AE86" s="19" t="n"/>
+      <c r="AF86" s="19" t="n"/>
+      <c r="AG86" s="19" t="n"/>
+      <c r="AH86" s="19" t="n"/>
+      <c r="AI86" s="19" t="n"/>
+      <c r="AJ86" s="19" t="n"/>
+      <c r="AK86" s="19" t="n"/>
+      <c r="AL86" s="22">
+        <f>SUM(G86:AK86)</f>
+        <v/>
+      </c>
+      <c r="AM86" s="23">
+        <f>SUM(C86,AL86)</f>
+        <v/>
+      </c>
+      <c r="AN86" s="24">
+        <f>E86*AM86</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="25.05" customHeight="1">
+      <c r="A87" s="37" t="inlineStr">
+        <is>
+          <t>17503</t>
+        </is>
+      </c>
+      <c r="B87" s="37" t="inlineStr">
+        <is>
+          <t>REFRESCO CRISTAL GASEOSA LA CASERA C/R 50 CL</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="38" t="inlineStr">
+        <is>
+          <t>BOTELLA</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0.45394</v>
+      </c>
+      <c r="F87" s="20">
+        <f>C87*E87</f>
+        <v/>
+      </c>
+      <c r="G87" s="19" t="n"/>
+      <c r="H87" s="19" t="n"/>
+      <c r="I87" s="19" t="n"/>
+      <c r="J87" s="19" t="n"/>
+      <c r="K87" s="19" t="n"/>
+      <c r="L87" s="19" t="n"/>
+      <c r="M87" s="19" t="n"/>
+      <c r="N87" s="19" t="n"/>
+      <c r="O87" s="19" t="n"/>
+      <c r="P87" s="19" t="n"/>
+      <c r="Q87" s="19" t="n"/>
+      <c r="R87" s="19" t="n"/>
+      <c r="S87" s="19" t="n"/>
+      <c r="T87" s="19" t="n"/>
+      <c r="U87" s="19" t="n"/>
+      <c r="V87" s="19" t="n"/>
+      <c r="W87" s="19" t="n"/>
+      <c r="X87" s="19" t="n"/>
+      <c r="Y87" s="19" t="n"/>
+      <c r="Z87" s="19" t="n"/>
+      <c r="AA87" s="19" t="n"/>
+      <c r="AB87" s="19" t="n"/>
+      <c r="AC87" s="19" t="n"/>
+      <c r="AD87" s="19" t="n"/>
+      <c r="AE87" s="19" t="n"/>
+      <c r="AF87" s="19" t="n"/>
+      <c r="AG87" s="19" t="n"/>
+      <c r="AH87" s="19" t="n"/>
+      <c r="AI87" s="19" t="n"/>
+      <c r="AJ87" s="19" t="n"/>
+      <c r="AK87" s="19" t="n"/>
+      <c r="AL87" s="22">
+        <f>SUM(G87:AK87)</f>
+        <v/>
+      </c>
+      <c r="AM87" s="23">
+        <f>SUM(C87,AL87)</f>
+        <v/>
+      </c>
+      <c r="AN87" s="24">
+        <f>E87*AM87</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="25.05" customHeight="1">
+      <c r="C88" s="3">
+        <f>SUM(C7:C87)</f>
+        <v/>
+      </c>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="10" t="inlineStr">
         <is>
           <t>ESTOCAJE  INICIAL</t>
         </is>
       </c>
-      <c r="F83" s="11">
-        <f>SUM(F7:F82)</f>
-        <v/>
-      </c>
-      <c r="G83" s="12" t="n"/>
-      <c r="H83" s="12" t="n"/>
-      <c r="I83" s="12" t="n"/>
-      <c r="J83" s="12" t="n"/>
-      <c r="K83" s="12" t="n"/>
-      <c r="L83" s="12" t="n"/>
-      <c r="M83" s="12" t="n"/>
-      <c r="N83" s="12" t="n"/>
-      <c r="O83" s="12" t="n"/>
-      <c r="P83" s="12" t="n"/>
-      <c r="Q83" s="12" t="n"/>
-      <c r="R83" s="12" t="n"/>
-      <c r="S83" s="12" t="n"/>
-      <c r="T83" s="12" t="n"/>
-      <c r="U83" s="12" t="n"/>
-      <c r="V83" s="12" t="n"/>
-      <c r="W83" s="12" t="n"/>
-      <c r="X83" s="12" t="n"/>
-      <c r="Y83" s="12" t="n"/>
-      <c r="Z83" s="12" t="n"/>
-      <c r="AA83" s="12" t="n"/>
-      <c r="AB83" s="12" t="n"/>
-      <c r="AC83" s="12" t="n"/>
-      <c r="AD83" s="12" t="n"/>
-      <c r="AE83" s="12" t="n"/>
-      <c r="AF83" s="12" t="n"/>
-      <c r="AG83" s="12" t="n"/>
-      <c r="AH83" s="12" t="n"/>
-      <c r="AI83" s="12" t="n"/>
-      <c r="AJ83" s="12" t="n"/>
-      <c r="AK83" s="12" t="n"/>
-      <c r="AL83" s="12">
-        <f>SUM(AL7:AL82)</f>
-        <v/>
-      </c>
-      <c r="AM83" s="12">
-        <f>SUM(AM7:AM82)</f>
-        <v/>
-      </c>
-      <c r="AN83" s="25">
-        <f>SUM(AN7:AN82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" ht="25.05" customHeight="1">
-      <c r="D84" s="9" t="n"/>
-      <c r="E84" s="12" t="n"/>
-      <c r="F84" s="12" t="n"/>
-      <c r="G84" s="12" t="n"/>
-      <c r="H84" s="12" t="n"/>
-      <c r="I84" s="12" t="n"/>
-      <c r="J84" s="12" t="n"/>
-      <c r="K84" s="12" t="n"/>
-      <c r="L84" s="12" t="n"/>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="12" t="n"/>
-      <c r="O84" s="12" t="n"/>
-      <c r="P84" s="12" t="n"/>
-      <c r="Q84" s="12" t="n"/>
-      <c r="R84" s="12" t="n"/>
-      <c r="S84" s="12" t="n"/>
-      <c r="T84" s="12" t="n"/>
-      <c r="U84" s="12" t="n"/>
-      <c r="V84" s="12" t="n"/>
-      <c r="W84" s="12" t="n"/>
-      <c r="X84" s="12" t="n"/>
-      <c r="Y84" s="12" t="n"/>
-      <c r="Z84" s="12" t="n"/>
-      <c r="AA84" s="12" t="n"/>
-      <c r="AB84" s="12" t="n"/>
-      <c r="AC84" s="12" t="n"/>
-      <c r="AD84" s="12" t="n"/>
-      <c r="AE84" s="12" t="n"/>
-      <c r="AF84" s="12" t="n"/>
-      <c r="AG84" s="12" t="n"/>
-      <c r="AH84" s="12" t="n"/>
-      <c r="AI84" s="12" t="n"/>
-      <c r="AJ84" s="12" t="n"/>
-      <c r="AK84" s="12" t="n"/>
-      <c r="AL84" s="12" t="n"/>
-      <c r="AM84" s="12" t="n"/>
-      <c r="AN84" s="12" t="n"/>
-    </row>
-    <row r="85" ht="25.05" customHeight="1">
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="12" t="n"/>
-      <c r="F85" s="12" t="n"/>
-      <c r="G85" s="12" t="n"/>
-      <c r="H85" s="12" t="n"/>
-      <c r="I85" s="12" t="n"/>
-      <c r="J85" s="12" t="n"/>
-      <c r="K85" s="12" t="n"/>
-      <c r="L85" s="12" t="n"/>
-      <c r="M85" s="12" t="n"/>
-      <c r="N85" s="12" t="n"/>
-      <c r="O85" s="12" t="n"/>
-      <c r="P85" s="12" t="n"/>
-      <c r="Q85" s="12" t="n"/>
-      <c r="R85" s="12" t="n"/>
-      <c r="S85" s="12" t="n"/>
-      <c r="T85" s="12" t="n"/>
-      <c r="U85" s="12" t="n"/>
-      <c r="V85" s="12" t="n"/>
-      <c r="W85" s="12" t="n"/>
-      <c r="X85" s="12" t="n"/>
-      <c r="Y85" s="12" t="n"/>
-      <c r="Z85" s="12" t="n"/>
-      <c r="AA85" s="12" t="n"/>
-      <c r="AB85" s="12" t="n"/>
-      <c r="AC85" s="12" t="n"/>
-      <c r="AD85" s="12" t="n"/>
-      <c r="AE85" s="12" t="n"/>
-      <c r="AF85" s="12" t="n"/>
-      <c r="AG85" s="12" t="n"/>
-      <c r="AH85" s="12" t="n"/>
-      <c r="AI85" s="12" t="n"/>
-      <c r="AJ85" s="12" t="n"/>
-      <c r="AK85" s="12" t="n"/>
-      <c r="AL85" s="12" t="n"/>
-      <c r="AM85" s="12" t="n"/>
-      <c r="AN85" s="12" t="n"/>
-    </row>
-    <row r="86" ht="25.05" customHeight="1">
-      <c r="D86" s="9" t="n"/>
-      <c r="E86" s="12" t="n"/>
-      <c r="F86" s="12" t="n"/>
-      <c r="G86" s="12" t="n"/>
-      <c r="H86" s="12" t="n"/>
-      <c r="I86" s="12" t="n"/>
-      <c r="J86" s="12" t="n"/>
-      <c r="K86" s="12" t="n"/>
-      <c r="L86" s="12" t="n"/>
-      <c r="M86" s="12" t="n"/>
-      <c r="N86" s="12" t="n"/>
-      <c r="O86" s="12" t="n"/>
-      <c r="P86" s="12" t="n"/>
-      <c r="Q86" s="12" t="n"/>
-      <c r="R86" s="12" t="n"/>
-      <c r="S86" s="12" t="n"/>
-      <c r="T86" s="12" t="n"/>
-      <c r="U86" s="12" t="n"/>
-      <c r="V86" s="12" t="n"/>
-      <c r="W86" s="12" t="n"/>
-      <c r="X86" s="12" t="n"/>
-      <c r="Y86" s="12" t="n"/>
-      <c r="Z86" s="12" t="n"/>
-      <c r="AA86" s="12" t="n"/>
-      <c r="AB86" s="12" t="n"/>
-      <c r="AC86" s="12" t="n"/>
-      <c r="AD86" s="12" t="n"/>
-      <c r="AE86" s="12" t="n"/>
-      <c r="AF86" s="12" t="n"/>
-      <c r="AG86" s="12" t="n"/>
-      <c r="AH86" s="12" t="n"/>
-      <c r="AI86" s="12" t="n"/>
-      <c r="AJ86" s="12" t="n"/>
-      <c r="AK86" s="12" t="n"/>
-      <c r="AL86" s="12" t="n"/>
-      <c r="AM86" s="12" t="n"/>
-    </row>
-    <row r="87" ht="25.05" customHeight="1">
-      <c r="D87" s="9" t="n"/>
-      <c r="F87" s="12" t="n"/>
-      <c r="G87" s="12" t="n"/>
-      <c r="H87" s="12" t="n"/>
-      <c r="I87" s="12" t="n"/>
-      <c r="J87" s="12" t="n"/>
-      <c r="K87" s="12" t="n"/>
-      <c r="L87" s="12" t="n"/>
-      <c r="M87" s="12" t="n"/>
-      <c r="N87" s="12" t="n"/>
-      <c r="O87" s="12" t="n"/>
-      <c r="P87" s="12" t="n"/>
-      <c r="Q87" s="12" t="n"/>
-      <c r="R87" s="12" t="n"/>
-      <c r="S87" s="12" t="n"/>
-      <c r="T87" s="12" t="n"/>
-      <c r="U87" s="12" t="n"/>
-      <c r="V87" s="12" t="n"/>
-      <c r="W87" s="12" t="n"/>
-      <c r="X87" s="12" t="n"/>
-      <c r="Y87" s="12" t="n"/>
-      <c r="Z87" s="12" t="n"/>
-      <c r="AA87" s="12" t="n"/>
-      <c r="AB87" s="12" t="n"/>
-      <c r="AC87" s="12" t="n"/>
-      <c r="AD87" s="12" t="n"/>
-      <c r="AE87" s="12" t="n"/>
-      <c r="AF87" s="12" t="n"/>
-      <c r="AG87" s="12" t="n"/>
-      <c r="AH87" s="12" t="n"/>
-      <c r="AI87" s="12" t="n"/>
-      <c r="AJ87" s="12" t="n"/>
-      <c r="AK87" s="12" t="n"/>
-      <c r="AL87" s="12" t="n"/>
-      <c r="AM87" s="12" t="n"/>
-      <c r="AN87" s="12" t="n"/>
-    </row>
-    <row r="88" ht="25.05" customHeight="1">
-      <c r="D88" s="9" t="n"/>
-      <c r="F88" s="12" t="n"/>
+      <c r="F88" s="11">
+        <f>SUM(F7:F87)</f>
+        <v/>
+      </c>
       <c r="G88" s="12" t="n"/>
       <c r="H88" s="12" t="n"/>
       <c r="I88" s="12" t="n"/>
@@ -6566,12 +6718,22 @@
       <c r="AI88" s="12" t="n"/>
       <c r="AJ88" s="12" t="n"/>
       <c r="AK88" s="12" t="n"/>
-      <c r="AL88" s="12" t="n"/>
-      <c r="AM88" s="12" t="n"/>
-      <c r="AN88" s="12" t="n"/>
+      <c r="AL88" s="12">
+        <f>SUM(AL7:AL87)</f>
+        <v/>
+      </c>
+      <c r="AM88" s="12">
+        <f>SUM(AM7:AM87)</f>
+        <v/>
+      </c>
+      <c r="AN88" s="25">
+        <f>SUM(AN7:AN87)</f>
+        <v/>
+      </c>
     </row>
     <row r="89" ht="25.05" customHeight="1">
       <c r="D89" s="9" t="n"/>
+      <c r="E89" s="12" t="n"/>
       <c r="F89" s="12" t="n"/>
       <c r="G89" s="12" t="n"/>
       <c r="H89" s="12" t="n"/>
@@ -6610,6 +6772,7 @@
     </row>
     <row r="90" ht="25.05" customHeight="1">
       <c r="D90" s="9" t="n"/>
+      <c r="E90" s="12" t="n"/>
       <c r="F90" s="12" t="n"/>
       <c r="G90" s="12" t="n"/>
       <c r="H90" s="12" t="n"/>
@@ -6648,6 +6811,7 @@
     </row>
     <row r="91" ht="25.05" customHeight="1">
       <c r="D91" s="9" t="n"/>
+      <c r="E91" s="12" t="n"/>
       <c r="F91" s="12" t="n"/>
       <c r="G91" s="12" t="n"/>
       <c r="H91" s="12" t="n"/>
@@ -6682,7 +6846,6 @@
       <c r="AK91" s="12" t="n"/>
       <c r="AL91" s="12" t="n"/>
       <c r="AM91" s="12" t="n"/>
-      <c r="AN91" s="12" t="n"/>
     </row>
     <row r="92" ht="25.05" customHeight="1">
       <c r="D92" s="9" t="n"/>
@@ -7218,18 +7381,193 @@
     </row>
     <row r="106" ht="25.05" customHeight="1">
       <c r="D106" s="9" t="n"/>
+      <c r="F106" s="12" t="n"/>
+      <c r="G106" s="12" t="n"/>
+      <c r="H106" s="12" t="n"/>
+      <c r="I106" s="12" t="n"/>
+      <c r="J106" s="12" t="n"/>
+      <c r="K106" s="12" t="n"/>
+      <c r="L106" s="12" t="n"/>
+      <c r="M106" s="12" t="n"/>
+      <c r="N106" s="12" t="n"/>
+      <c r="O106" s="12" t="n"/>
+      <c r="P106" s="12" t="n"/>
+      <c r="Q106" s="12" t="n"/>
+      <c r="R106" s="12" t="n"/>
+      <c r="S106" s="12" t="n"/>
+      <c r="T106" s="12" t="n"/>
+      <c r="U106" s="12" t="n"/>
+      <c r="V106" s="12" t="n"/>
+      <c r="W106" s="12" t="n"/>
+      <c r="X106" s="12" t="n"/>
+      <c r="Y106" s="12" t="n"/>
+      <c r="Z106" s="12" t="n"/>
+      <c r="AA106" s="12" t="n"/>
+      <c r="AB106" s="12" t="n"/>
+      <c r="AC106" s="12" t="n"/>
+      <c r="AD106" s="12" t="n"/>
+      <c r="AE106" s="12" t="n"/>
+      <c r="AF106" s="12" t="n"/>
+      <c r="AG106" s="12" t="n"/>
+      <c r="AH106" s="12" t="n"/>
+      <c r="AI106" s="12" t="n"/>
+      <c r="AJ106" s="12" t="n"/>
+      <c r="AK106" s="12" t="n"/>
+      <c r="AL106" s="12" t="n"/>
+      <c r="AM106" s="12" t="n"/>
+      <c r="AN106" s="12" t="n"/>
     </row>
     <row r="107" ht="25.05" customHeight="1">
       <c r="D107" s="9" t="n"/>
+      <c r="F107" s="12" t="n"/>
+      <c r="G107" s="12" t="n"/>
+      <c r="H107" s="12" t="n"/>
+      <c r="I107" s="12" t="n"/>
+      <c r="J107" s="12" t="n"/>
+      <c r="K107" s="12" t="n"/>
+      <c r="L107" s="12" t="n"/>
+      <c r="M107" s="12" t="n"/>
+      <c r="N107" s="12" t="n"/>
+      <c r="O107" s="12" t="n"/>
+      <c r="P107" s="12" t="n"/>
+      <c r="Q107" s="12" t="n"/>
+      <c r="R107" s="12" t="n"/>
+      <c r="S107" s="12" t="n"/>
+      <c r="T107" s="12" t="n"/>
+      <c r="U107" s="12" t="n"/>
+      <c r="V107" s="12" t="n"/>
+      <c r="W107" s="12" t="n"/>
+      <c r="X107" s="12" t="n"/>
+      <c r="Y107" s="12" t="n"/>
+      <c r="Z107" s="12" t="n"/>
+      <c r="AA107" s="12" t="n"/>
+      <c r="AB107" s="12" t="n"/>
+      <c r="AC107" s="12" t="n"/>
+      <c r="AD107" s="12" t="n"/>
+      <c r="AE107" s="12" t="n"/>
+      <c r="AF107" s="12" t="n"/>
+      <c r="AG107" s="12" t="n"/>
+      <c r="AH107" s="12" t="n"/>
+      <c r="AI107" s="12" t="n"/>
+      <c r="AJ107" s="12" t="n"/>
+      <c r="AK107" s="12" t="n"/>
+      <c r="AL107" s="12" t="n"/>
+      <c r="AM107" s="12" t="n"/>
+      <c r="AN107" s="12" t="n"/>
     </row>
     <row r="108" ht="25.05" customHeight="1">
       <c r="D108" s="9" t="n"/>
+      <c r="F108" s="12" t="n"/>
+      <c r="G108" s="12" t="n"/>
+      <c r="H108" s="12" t="n"/>
+      <c r="I108" s="12" t="n"/>
+      <c r="J108" s="12" t="n"/>
+      <c r="K108" s="12" t="n"/>
+      <c r="L108" s="12" t="n"/>
+      <c r="M108" s="12" t="n"/>
+      <c r="N108" s="12" t="n"/>
+      <c r="O108" s="12" t="n"/>
+      <c r="P108" s="12" t="n"/>
+      <c r="Q108" s="12" t="n"/>
+      <c r="R108" s="12" t="n"/>
+      <c r="S108" s="12" t="n"/>
+      <c r="T108" s="12" t="n"/>
+      <c r="U108" s="12" t="n"/>
+      <c r="V108" s="12" t="n"/>
+      <c r="W108" s="12" t="n"/>
+      <c r="X108" s="12" t="n"/>
+      <c r="Y108" s="12" t="n"/>
+      <c r="Z108" s="12" t="n"/>
+      <c r="AA108" s="12" t="n"/>
+      <c r="AB108" s="12" t="n"/>
+      <c r="AC108" s="12" t="n"/>
+      <c r="AD108" s="12" t="n"/>
+      <c r="AE108" s="12" t="n"/>
+      <c r="AF108" s="12" t="n"/>
+      <c r="AG108" s="12" t="n"/>
+      <c r="AH108" s="12" t="n"/>
+      <c r="AI108" s="12" t="n"/>
+      <c r="AJ108" s="12" t="n"/>
+      <c r="AK108" s="12" t="n"/>
+      <c r="AL108" s="12" t="n"/>
+      <c r="AM108" s="12" t="n"/>
+      <c r="AN108" s="12" t="n"/>
     </row>
     <row r="109" ht="25.05" customHeight="1">
       <c r="D109" s="9" t="n"/>
+      <c r="F109" s="12" t="n"/>
+      <c r="G109" s="12" t="n"/>
+      <c r="H109" s="12" t="n"/>
+      <c r="I109" s="12" t="n"/>
+      <c r="J109" s="12" t="n"/>
+      <c r="K109" s="12" t="n"/>
+      <c r="L109" s="12" t="n"/>
+      <c r="M109" s="12" t="n"/>
+      <c r="N109" s="12" t="n"/>
+      <c r="O109" s="12" t="n"/>
+      <c r="P109" s="12" t="n"/>
+      <c r="Q109" s="12" t="n"/>
+      <c r="R109" s="12" t="n"/>
+      <c r="S109" s="12" t="n"/>
+      <c r="T109" s="12" t="n"/>
+      <c r="U109" s="12" t="n"/>
+      <c r="V109" s="12" t="n"/>
+      <c r="W109" s="12" t="n"/>
+      <c r="X109" s="12" t="n"/>
+      <c r="Y109" s="12" t="n"/>
+      <c r="Z109" s="12" t="n"/>
+      <c r="AA109" s="12" t="n"/>
+      <c r="AB109" s="12" t="n"/>
+      <c r="AC109" s="12" t="n"/>
+      <c r="AD109" s="12" t="n"/>
+      <c r="AE109" s="12" t="n"/>
+      <c r="AF109" s="12" t="n"/>
+      <c r="AG109" s="12" t="n"/>
+      <c r="AH109" s="12" t="n"/>
+      <c r="AI109" s="12" t="n"/>
+      <c r="AJ109" s="12" t="n"/>
+      <c r="AK109" s="12" t="n"/>
+      <c r="AL109" s="12" t="n"/>
+      <c r="AM109" s="12" t="n"/>
+      <c r="AN109" s="12" t="n"/>
     </row>
     <row r="110" ht="25.05" customHeight="1">
       <c r="D110" s="9" t="n"/>
+      <c r="F110" s="12" t="n"/>
+      <c r="G110" s="12" t="n"/>
+      <c r="H110" s="12" t="n"/>
+      <c r="I110" s="12" t="n"/>
+      <c r="J110" s="12" t="n"/>
+      <c r="K110" s="12" t="n"/>
+      <c r="L110" s="12" t="n"/>
+      <c r="M110" s="12" t="n"/>
+      <c r="N110" s="12" t="n"/>
+      <c r="O110" s="12" t="n"/>
+      <c r="P110" s="12" t="n"/>
+      <c r="Q110" s="12" t="n"/>
+      <c r="R110" s="12" t="n"/>
+      <c r="S110" s="12" t="n"/>
+      <c r="T110" s="12" t="n"/>
+      <c r="U110" s="12" t="n"/>
+      <c r="V110" s="12" t="n"/>
+      <c r="W110" s="12" t="n"/>
+      <c r="X110" s="12" t="n"/>
+      <c r="Y110" s="12" t="n"/>
+      <c r="Z110" s="12" t="n"/>
+      <c r="AA110" s="12" t="n"/>
+      <c r="AB110" s="12" t="n"/>
+      <c r="AC110" s="12" t="n"/>
+      <c r="AD110" s="12" t="n"/>
+      <c r="AE110" s="12" t="n"/>
+      <c r="AF110" s="12" t="n"/>
+      <c r="AG110" s="12" t="n"/>
+      <c r="AH110" s="12" t="n"/>
+      <c r="AI110" s="12" t="n"/>
+      <c r="AJ110" s="12" t="n"/>
+      <c r="AK110" s="12" t="n"/>
+      <c r="AL110" s="12" t="n"/>
+      <c r="AM110" s="12" t="n"/>
+      <c r="AN110" s="12" t="n"/>
     </row>
     <row r="111" ht="25.05" customHeight="1">
       <c r="D111" s="9" t="n"/>
@@ -9909,6 +10247,21 @@
     </row>
     <row r="1003">
       <c r="D1003" s="9" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="D1004" s="9" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="D1005" s="9" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="D1006" s="9" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="D1007" s="9" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="D1008" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:F6"/>
